--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="430">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1587,10 +1587,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>crid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>luk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1688,6 +1684,54 @@
   </si>
   <si>
     <t>任務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昏眩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成傷害的{#num}轉換為生命值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2265,13 +2309,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>404</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3308,10 +3352,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -3624,7 +3668,7 @@
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="92" style="7" customWidth="1"/>
+    <col min="3" max="3" width="65.5546875" style="7" customWidth="1"/>
     <col min="4" max="4" width="23.21875" style="8" customWidth="1"/>
     <col min="5" max="5" width="12.21875" style="8" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="6"/>
@@ -3666,7 +3710,7 @@
         <v>304</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3677,7 +3721,7 @@
         <v>308</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3688,7 +3732,7 @@
         <v>309</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3699,18 +3743,18 @@
         <v>310</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>395</v>
-      </c>
       <c r="C7" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3794,7 +3838,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>314</v>
@@ -4043,13 +4087,51 @@
         <v>380</v>
       </c>
     </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
     <row r="48" spans="1:3">
+      <c r="A48" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>423</v>
+      </c>
       <c r="C48" s="9"/>
     </row>
-    <row r="51" spans="3:3">
-      <c r="C51" s="9"/>
-    </row>
-    <row r="52" spans="3:3">
+    <row r="50" spans="1:3">
+      <c r="A50" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="C52" s="9"/>
     </row>
   </sheetData>
@@ -4200,7 +4282,7 @@
         <v>382</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4213,10 +4295,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>401</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4270,42 +4352,42 @@
     <row r="3" spans="1:5" ht="16.2" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>417</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>413</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>407</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>409</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="432">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1732,6 +1732,14 @@
   </si>
   <si>
     <t>造成傷害的{#num}轉換為生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3663,7 +3671,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
@@ -4095,44 +4103,52 @@
         <v>419</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>421</v>
+    <row r="46" spans="1:3">
+      <c r="A46" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="C48" s="9"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>425</v>
-      </c>
+      <c r="C49" s="9"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="C52" s="9"/>
+    <row r="53" spans="1:3">
+      <c r="C53" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,14 @@
     <sheet name="tag" sheetId="6" r:id="rId6"/>
     <sheet name="other" sheetId="7" r:id="rId7"/>
     <sheet name="quest" sheetId="8" r:id="rId8"/>
+    <sheet name="ability" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="449">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1740,6 +1741,74 @@
   </si>
   <si>
     <t>施法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支援</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偷竊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>General</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Archery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Support</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enhancement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劍技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stealing</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4410,4 +4479,117 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="15.6">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="15.6">
+      <c r="B2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -1808,7 +1808,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stealing</t>
+    <t>steal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,14 @@
     <sheet name="other" sheetId="7" r:id="rId7"/>
     <sheet name="quest" sheetId="8" r:id="rId8"/>
     <sheet name="ability" sheetId="9" r:id="rId9"/>
+    <sheet name="option" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="431">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -704,10 +705,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>picks up</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>take</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -720,74 +717,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_pickup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_drop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丟棄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_space_full</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_kill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>擊殺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kills</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_die</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>died</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_buy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_sell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>購買</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出售</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buys</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sells</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_not_enough_gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -801,18 +734,6 @@
   </si>
   <si>
     <t>Not enough coins !!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_drink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>喝水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drinks water</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1809,6 +1730,14 @@
   </si>
   <si>
     <t>steal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pickup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pickup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2293,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
@@ -2386,13 +2315,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2540,13 +2469,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2579,7 +2508,7 @@
         <v>112</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>113</v>
@@ -2593,7 +2522,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>115</v>
@@ -2607,7 +2536,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>118</v>
@@ -2637,13 +2566,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="D32" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2802,173 +2731,283 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="6" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="6" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="6" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="6" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="6" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.21875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3017,7 +3056,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3025,10 +3064,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3053,7 +3092,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3061,10 +3100,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3072,10 +3111,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3083,7 +3122,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>31</v>
@@ -3101,7 +3140,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3109,10 +3148,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3123,7 +3162,7 @@
         <v>30</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3135,7 +3174,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>40</v>
@@ -3172,10 +3211,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3220,10 +3259,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3246,7 +3285,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>34</v>
@@ -3261,10 +3300,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3272,10 +3311,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -3324,16 +3363,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3341,86 +3380,86 @@
     </row>
     <row r="5" spans="1:5" ht="32.4">
       <c r="A5" s="1" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="32.4">
       <c r="A6" s="1" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32.4">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32.4">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32.4">
       <c r="A9" s="2" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="32.4">
       <c r="A10" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3429,10 +3468,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -3534,13 +3573,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3548,27 +3587,27 @@
         <v>50</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="6" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3576,72 +3615,72 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="13" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="13" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="13" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3781,57 +3820,57 @@
     </row>
     <row r="3" spans="1:5" ht="16.2" thickTop="1">
       <c r="A3" s="6" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3840,99 +3879,99 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="C9" s="22"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>114</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>117</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3941,55 +3980,55 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3998,46 +4037,46 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="C25" s="22"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="C26" s="22"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C27" s="22"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C29" s="22"/>
     </row>
@@ -4047,13 +4086,13 @@
     </row>
     <row r="31" spans="1:3" ht="31.2">
       <c r="A31" s="6" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>112</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="31.2">
@@ -4064,7 +4103,7 @@
         <v>120</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="31.2">
@@ -4075,7 +4114,7 @@
         <v>122</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4084,136 +4123,136 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="6" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="6" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C49" s="9"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="6" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4266,26 +4305,26 @@
     <row r="3" spans="1:5" ht="16.8" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B4" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="B5" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B6" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -4337,18 +4376,18 @@
     <row r="3" spans="1:5" ht="16.2" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4361,29 +4400,29 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4437,42 +4476,42 @@
     <row r="3" spans="1:5" ht="16.2" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -4518,74 +4557,74 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="B3" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="B4" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="B6" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="B9" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="B10" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="B12" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="437">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1738,6 +1738,30 @@
   </si>
   <si>
     <t>Pickup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上鎖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解鎖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlock</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2223,14 +2247,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.21875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.25" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2500,7 +2524,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="31.2">
+    <row r="26" spans="1:4" ht="31.5">
       <c r="A26" s="6" t="s">
         <v>111</v>
       </c>
@@ -2826,15 +2850,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="50.21875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="7" customWidth="1"/>
+    <col min="3" max="3" width="50.25" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3003,6 +3027,28 @@
       </c>
       <c r="D15" s="8" t="s">
         <v>430</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -3014,13 +3060,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3327,13 +3373,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="19.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3378,7 +3424,7 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="32.4">
+    <row r="5" spans="1:5" ht="33">
       <c r="A5" s="1" t="s">
         <v>218</v>
       </c>
@@ -3392,7 +3438,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="32.4">
+    <row r="6" spans="1:5" ht="33">
       <c r="A6" s="1" t="s">
         <v>222</v>
       </c>
@@ -3406,7 +3452,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="32.4">
+    <row r="7" spans="1:5" ht="33">
       <c r="A7" s="2" t="s">
         <v>230</v>
       </c>
@@ -3420,7 +3466,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="32.4">
+    <row r="8" spans="1:5" ht="33">
       <c r="A8" s="2" t="s">
         <v>229</v>
       </c>
@@ -3434,7 +3480,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="32.4">
+    <row r="9" spans="1:5" ht="33">
       <c r="A9" s="2" t="s">
         <v>228</v>
       </c>
@@ -3448,7 +3494,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32.4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>253</v>
       </c>
@@ -3561,14 +3607,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16" style="6" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="14.875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="42.5" style="12" customWidth="1"/>
+    <col min="4" max="4" width="19.625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3596,7 +3642,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="6" t="s">
         <v>190</v>
       </c>
@@ -3780,14 +3826,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="65.5546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="13.25" style="7" customWidth="1"/>
+    <col min="3" max="3" width="65.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3803,7 +3849,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="16.2" thickBot="1">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>4</v>
@@ -3818,7 +3864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.2" thickTop="1">
+    <row r="3" spans="1:5" ht="16.5" thickTop="1">
       <c r="A3" s="6" t="s">
         <v>283</v>
       </c>
@@ -4084,7 +4130,7 @@
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
     </row>
-    <row r="31" spans="1:3" ht="31.2">
+    <row r="31" spans="1:3" ht="31.5">
       <c r="A31" s="6" t="s">
         <v>282</v>
       </c>
@@ -4095,7 +4141,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="31.2">
+    <row r="32" spans="1:3" ht="31.5">
       <c r="A32" s="6" t="s">
         <v>119</v>
       </c>
@@ -4106,7 +4152,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="31.2">
+    <row r="33" spans="1:3" ht="31.5">
       <c r="A33" s="6" t="s">
         <v>121</v>
       </c>
@@ -4268,10 +4314,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="5" max="5" width="38.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="5" max="5" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4287,7 +4333,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="16.8" thickBot="1">
+    <row r="2" spans="1:5" ht="17.25" thickBot="1">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>4</v>
@@ -4302,7 +4348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.8" thickTop="1"/>
+    <row r="3" spans="1:5" ht="17.25" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>334</v>
@@ -4336,13 +4382,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="6"/>
-    <col min="3" max="3" width="28.5546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="6"/>
-    <col min="5" max="5" width="38.88671875" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="2" width="8.875" style="6"/>
+    <col min="3" max="3" width="28.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="6"/>
+    <col min="5" max="5" width="38.875" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4358,7 +4404,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="16.2" thickBot="1">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>4</v>
@@ -4373,7 +4419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.2" thickTop="1"/>
+    <row r="3" spans="1:5" ht="16.5" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>336</v>
@@ -4435,14 +4481,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="6"/>
-    <col min="3" max="3" width="28.5546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="6"/>
-    <col min="5" max="5" width="38.88671875" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="12.625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="6"/>
+    <col min="3" max="3" width="28.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="6"/>
+    <col min="5" max="5" width="38.875" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4458,7 +4504,7 @@
       </c>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="16.2" thickBot="1">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>4</v>
@@ -4473,7 +4519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.2" thickTop="1"/>
+    <row r="3" spans="1:5" ht="16.5" thickTop="1"/>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>396</v>
@@ -4523,12 +4569,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" ht="15.6">
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="15.75">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -4541,7 +4587,7 @@
       </c>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="15.6">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="15.75">
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>

--- a/xls/local.xlsx
+++ b/xls/local.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="440">
   <si>
     <t>bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1762,6 +1762,18 @@
   </si>
   <si>
     <t>Unlock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>butcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Butcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解剖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2850,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
@@ -3049,6 +3061,17 @@
       </c>
       <c r="D17" s="8" t="s">
         <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
